--- a/data/stx_xlsx/VOLCARb.ST.xlsx
+++ b/data/stx_xlsx/VOLCARb.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="428">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -805,6 +805,9 @@
   </si>
   <si>
     <t>Othernon-currentprovisions</t>
+  </si>
+  <si>
+    <t>Liabilities to credit institutions (Do not use)</t>
   </si>
   <si>
     <t>Liabilities related to finance lease contracts - Long term</t>
@@ -1425,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1506,6 +1509,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -11982,8 +11988,8 @@
       </c>
     </row>
     <row r="105" ht="15.0" customHeight="1">
-      <c r="A105" s="14" t="s">
-        <v>241</v>
+      <c r="A105" s="27" t="s">
+        <v>262</v>
       </c>
       <c r="B105" s="18">
         <v>7351.38</v>
@@ -12022,8 +12028,8 @@
       <c r="P105" s="15"/>
     </row>
     <row r="106" ht="15.0" customHeight="1">
-      <c r="A106" s="14" t="s">
-        <v>241</v>
+      <c r="A106" s="27" t="s">
+        <v>262</v>
       </c>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -12059,7 +12065,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -12085,7 +12091,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B108" s="15">
         <v>23668.09</v>
@@ -12151,7 +12157,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B110" s="18">
         <v>276.65</v>
@@ -12191,7 +12197,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B111" s="18">
         <v>7341.54</v>
@@ -12241,7 +12247,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -12265,7 +12271,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B113" s="18">
         <v>7341.54</v>
@@ -12305,7 +12311,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B114" s="18">
         <v>9409.28</v>
@@ -12341,7 +12347,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B115" s="18">
         <v>5855.51</v>
@@ -12375,7 +12381,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B116" s="17">
         <v>80413.54</v>
@@ -12425,7 +12431,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B117" s="17">
         <v>245804.75</v>
@@ -12475,7 +12481,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B118" s="19">
         <v>66.7</v>
@@ -12515,7 +12521,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B119" s="15">
         <v>34612.59</v>
@@ -12555,7 +12561,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B120" s="18">
         <v>9241.98</v>
@@ -12595,7 +12601,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B121" s="18">
         <v>1095.65</v>
@@ -12635,7 +12641,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B122" s="18">
         <v>4989.49</v>
@@ -12675,7 +12681,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B123" s="15">
         <v>110819.57</v>
@@ -12715,7 +12721,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -12745,7 +12751,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B125" s="17">
         <v>160825.99</v>
@@ -12841,7 +12847,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B127" s="23">
         <v>1420.41</v>
@@ -12887,7 +12893,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B128" s="17">
         <v>162246.4</v>
@@ -12937,7 +12943,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B129" s="17">
         <v>408051.15</v>
@@ -12987,7 +12993,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B130" s="18">
         <v>2964.63</v>
@@ -13037,7 +13043,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B131" s="19">
         <v>14.89</v>
@@ -13087,7 +13093,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B132" s="18">
         <v>2979.52</v>
@@ -13137,7 +13143,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -13209,7 +13215,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B136" s="18">
         <v>2648.38</v>
@@ -13245,7 +13251,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B137" s="15">
         <v>28320.79</v>
@@ -13281,7 +13287,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B138" s="18">
         <v>2698.68</v>
@@ -13317,7 +13323,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -13347,7 +13353,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -13381,7 +13387,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -13415,7 +13421,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -13443,7 +13449,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -13471,7 +13477,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -13499,7 +13505,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -13533,7 +13539,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -13567,7 +13573,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B147" s="18">
         <v>1640.2</v>
@@ -13599,7 +13605,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -13621,7 +13627,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -13645,7 +13651,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B150" s="18">
         <v>2979.52</v>
@@ -13695,7 +13701,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B151" s="19">
         <v>14.89</v>
@@ -13745,7 +13751,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B152" s="18">
         <v>2964.63</v>
@@ -13795,7 +13801,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B153" s="19">
         <v>1.0</v>
@@ -13845,7 +13851,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -13871,7 +13877,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -13897,7 +13903,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -13923,7 +13929,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -14812,7 +14818,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15107,49 +15113,49 @@
         <v>37</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15204,7 +15210,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15274,7 +15280,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B20" s="18">
         <v>320.93</v>
@@ -15324,7 +15330,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -15360,7 +15366,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B22" s="15">
         <v>25361.65</v>
@@ -15394,7 +15400,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B23" s="18">
         <v>217.13</v>
@@ -15426,7 +15432,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B24" s="18">
         <v>2043.12</v>
@@ -15476,7 +15482,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B25" s="21">
         <v>-1628.99</v>
@@ -15526,7 +15532,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B26" s="21">
         <v>-2079.14</v>
@@ -15576,7 +15582,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B27" s="21">
         <v>-3944.32</v>
@@ -15626,7 +15632,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B28" s="18">
         <v>6652.6</v>
@@ -15676,7 +15682,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -15700,7 +15706,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -15724,7 +15730,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -15772,7 +15778,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -15796,7 +15802,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -15820,7 +15826,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -15844,7 +15850,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -15868,7 +15874,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -15892,7 +15898,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -15916,7 +15922,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -15940,7 +15946,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B40" s="18">
         <v>2492.21</v>
@@ -15990,7 +15996,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B41" s="22">
         <v>-88.97</v>
@@ -16040,7 +16046,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -16072,7 +16078,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B43" s="18">
         <v>7631.27</v>
@@ -16122,7 +16128,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B44" s="21">
         <v>-1977.46</v>
@@ -16172,7 +16178,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B45" s="18">
         <v>682.1</v>
@@ -16210,7 +16216,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B46" s="18">
         <v>991.38</v>
@@ -16260,7 +16266,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B47" s="18">
         <v>9730.53</v>
@@ -16292,7 +16298,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B48" s="17">
         <v>36673.51</v>
@@ -16342,7 +16348,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B49" s="18">
         <v>296.57</v>
@@ -16392,7 +16398,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B50" s="21">
         <v>-2888.34</v>
@@ -16422,7 +16428,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -16452,7 +16458,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B52" s="20">
         <v>-18272.68</v>
@@ -16502,7 +16508,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B53" s="20">
         <v>-24175.39</v>
@@ -16552,7 +16558,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B54" s="18">
         <v>923.59</v>
@@ -16602,7 +16608,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -16626,7 +16632,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -16654,7 +16660,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B57" s="18">
         <v>8172.5</v>
@@ -16678,7 +16684,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="21">
@@ -16702,7 +16708,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -16726,7 +16732,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B60" s="19">
         <v>76.26</v>
@@ -16766,7 +16772,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B61" s="18">
         <v>1787.87</v>
@@ -16788,42 +16794,42 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="B62" s="27">
+        <v>352</v>
+      </c>
+      <c r="B62" s="28">
         <v>-34079.62</v>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="28">
         <v>-47031.05</v>
       </c>
-      <c r="D62" s="27">
+      <c r="D62" s="28">
         <v>-51597.12</v>
       </c>
-      <c r="E62" s="27">
+      <c r="E62" s="28">
         <v>-37680.84</v>
       </c>
-      <c r="F62" s="27">
+      <c r="F62" s="28">
         <v>-34813.67</v>
       </c>
-      <c r="G62" s="27">
+      <c r="G62" s="28">
         <v>-21496.19</v>
       </c>
-      <c r="H62" s="27">
+      <c r="H62" s="28">
         <v>-19357.07</v>
       </c>
-      <c r="I62" s="27">
+      <c r="I62" s="28">
         <v>-20658.49</v>
       </c>
-      <c r="J62" s="27">
+      <c r="J62" s="28">
         <v>-27823.49</v>
       </c>
-      <c r="K62" s="27">
+      <c r="K62" s="28">
         <v>-19978.88</v>
       </c>
-      <c r="L62" s="27">
+      <c r="L62" s="28">
         <v>-14668.57</v>
       </c>
-      <c r="M62" s="27">
+      <c r="M62" s="28">
         <v>-12497.3</v>
       </c>
       <c r="N62" s="25">
@@ -16838,7 +16844,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B63" s="18">
         <v>5239.68</v>
@@ -16888,7 +16894,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B64" s="18">
         <v>5799.98</v>
@@ -16930,7 +16936,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B65" s="21">
         <v>-1727.49</v>
@@ -16980,7 +16986,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B66" s="21">
         <v>-2232.72</v>
@@ -17014,7 +17020,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -17042,7 +17048,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -17066,7 +17072,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15">
@@ -17108,7 +17114,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B70" s="18">
         <v>1054.93</v>
@@ -17158,7 +17164,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -17186,7 +17192,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B72" s="21">
         <v>-6071.12</v>
@@ -17218,7 +17224,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -17244,7 +17250,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -17266,7 +17272,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -17292,7 +17298,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -17314,7 +17320,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -17352,7 +17358,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B78" s="22">
         <v>-1.06</v>
@@ -17384,7 +17390,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B79" s="21">
         <v>-231.96</v>
@@ -17408,7 +17414,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B80" s="23">
         <v>1830.23</v>
@@ -17458,7 +17464,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B81" s="15">
         <v>61642.0</v>
@@ -17508,7 +17514,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B82" s="21">
         <v>-3162.66</v>
@@ -17558,7 +17564,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B83" s="15">
         <v>62944.32</v>
@@ -17608,7 +17614,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B84" s="18">
         <v>4424.12</v>
@@ -17658,7 +17664,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B85" s="23">
         <v>1261.46</v>
@@ -17666,7 +17672,7 @@
       <c r="C85" s="23">
         <v>8656.68</v>
       </c>
-      <c r="D85" s="27">
+      <c r="D85" s="28">
         <v>-15806.98</v>
       </c>
       <c r="E85" s="23">
@@ -18643,7 +18649,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19035,7 +19041,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19104,1276 +19110,1276 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>376</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="B21" s="32">
         <v>79736.02</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>61214.86</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>74010.4</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>97517.13</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>176806.56</v>
       </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="31"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>377</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="B22" s="32">
         <v>107389.8</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B24" s="32">
         <v>100020.92</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>73456.39</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>91515.02</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>124505.08</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>209491.66</v>
       </c>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="B25" s="32">
         <v>131460.28</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>381</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="B27" s="33">
         <v>33.57</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>24.65</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>30.71</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>41.79</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>70.31</v>
       </c>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>382</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="B28" s="33">
         <v>44.12</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>384</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>384</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" s="34">
         <v>-5.98</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>3.28</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>4.07</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>1.12</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>3.44</v>
       </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="B31" s="34">
+      <c r="A31" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="B31" s="35">
         <v>1.57</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="B33" s="34">
+      <c r="A33" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="B33" s="35">
         <v>0.0</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>0.0</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>0.0</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>0.0</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>0.0</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>388</v>
-      </c>
-      <c r="B34" s="34">
+      <c r="A34" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="B34" s="35">
         <v>0.0</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="B35" s="34">
+      <c r="A35" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="B35" s="35">
         <v>0.0</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <v>0.0</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>0.0</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>0.0</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>0.0</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>390</v>
-      </c>
-      <c r="B36" s="34">
+      <c r="A36" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="B36" s="35">
         <v>0.0</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>391</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>392</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="B38" s="33">
         <v>0.62</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>0.52</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>0.72</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>1.16</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>2.38</v>
       </c>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="31"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="31"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>393</v>
-      </c>
-      <c r="B39" s="32">
+      <c r="A39" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="B39" s="33">
         <v>0.98</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>395</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>395</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="B41" s="33">
         <v>1.42</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>1.33</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>1.68</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>2.32</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>4.64</v>
       </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>396</v>
-      </c>
-      <c r="B42" s="32">
+      <c r="A42" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="B42" s="33">
         <v>2.18</v>
       </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>397</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>398</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="B44" s="33">
         <v>0.26</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>0.18</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>0.23</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>0.4</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>0.67</v>
       </c>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="31"/>
-      <c r="N44" s="31"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="31"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="B45" s="32">
+      <c r="A45" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="B45" s="33">
         <v>0.33</v>
       </c>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="31"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="32">
+      <c r="A47" s="31" t="s">
+        <v>402</v>
+      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="33">
         <v>30.53</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="33">
         <v>24.56</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="33">
         <v>88.96</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="33">
         <v>29.05</v>
       </c>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="B48" s="33">
         <v>63.52</v>
       </c>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>403</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>404</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="31" t="s">
+        <v>405</v>
+      </c>
+      <c r="B50" s="33">
         <v>4.35</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>1.85</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>2.9</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>4.0</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <v>6.6</v>
       </c>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="31"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>405</v>
-      </c>
-      <c r="B51" s="32">
+      <c r="A51" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="B51" s="33">
         <v>3.84</v>
       </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-      <c r="N51" s="31"/>
-      <c r="O51" s="31"/>
-      <c r="P51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+      <c r="P51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>406</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
+      <c r="A52" s="29" t="s">
+        <v>407</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>407</v>
-      </c>
-      <c r="B53" s="35">
+      <c r="A53" s="31" t="s">
+        <v>408</v>
+      </c>
+      <c r="B53" s="36">
         <v>524.16</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>4.64</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="33">
         <v>6.97</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="33">
         <v>8.49</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="33">
         <v>15.56</v>
       </c>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>408</v>
-      </c>
-      <c r="B54" s="32">
+      <c r="A54" s="31" t="s">
+        <v>409</v>
+      </c>
+      <c r="B54" s="33">
         <v>10.36</v>
       </c>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
-      <c r="N54" s="31"/>
-      <c r="O54" s="31"/>
-      <c r="P54" s="31"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="N54" s="32"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
+      <c r="A55" s="29" t="s">
+        <v>410</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>410</v>
-      </c>
-      <c r="B56" s="32">
+      <c r="A56" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="B56" s="33">
         <v>3.68</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>3.84</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <v>6.21</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <v>12.18</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="33">
         <v>14.75</v>
       </c>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="31"/>
-      <c r="K56" s="31"/>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-      <c r="N56" s="31"/>
-      <c r="O56" s="31"/>
-      <c r="P56" s="31"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B57" s="32">
+      <c r="A57" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="B57" s="33">
         <v>0.98</v>
       </c>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-      <c r="N57" s="31"/>
-      <c r="O57" s="31"/>
-      <c r="P57" s="31"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
+      <c r="N57" s="32"/>
+      <c r="O57" s="32"/>
+      <c r="P57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
+      <c r="A58" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B59" s="36">
+      <c r="A59" s="31" t="s">
+        <v>414</v>
+      </c>
+      <c r="B59" s="37">
         <v>-5.3</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>0.26</v>
       </c>
-      <c r="D59" s="36">
+      <c r="D59" s="37">
         <v>-0.43</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="33">
         <v>0.67</v>
       </c>
-      <c r="F59" s="36">
+      <c r="F59" s="37">
         <v>-0.32</v>
       </c>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="B60" s="36">
+      <c r="A60" s="31" t="s">
+        <v>415</v>
+      </c>
+      <c r="B60" s="37">
         <v>-0.16</v>
       </c>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="31"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="31"/>
-      <c r="K60" s="31"/>
-      <c r="L60" s="31"/>
-      <c r="M60" s="31"/>
-      <c r="N60" s="31"/>
-      <c r="O60" s="31"/>
-      <c r="P60" s="31"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="32"/>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32"/>
+      <c r="N60" s="32"/>
+      <c r="O60" s="32"/>
+      <c r="P60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>415</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
+      <c r="A61" s="29" t="s">
+        <v>416</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="B62" s="32">
+      <c r="A62" s="31" t="s">
+        <v>417</v>
+      </c>
+      <c r="B62" s="33">
         <v>0.2</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>0.15</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>0.18</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>0.31</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>0.64</v>
       </c>
-      <c r="G62" s="31"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="31"/>
-      <c r="K62" s="31"/>
-      <c r="L62" s="31"/>
-      <c r="M62" s="31"/>
-      <c r="N62" s="31"/>
-      <c r="O62" s="31"/>
-      <c r="P62" s="31"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32"/>
+      <c r="N62" s="32"/>
+      <c r="O62" s="32"/>
+      <c r="P62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>417</v>
-      </c>
-      <c r="B63" s="32">
+      <c r="A63" s="31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B63" s="33">
         <v>0.28</v>
       </c>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="31"/>
-      <c r="I63" s="31"/>
-      <c r="J63" s="31"/>
-      <c r="K63" s="31"/>
-      <c r="L63" s="31"/>
-      <c r="M63" s="31"/>
-      <c r="N63" s="31"/>
-      <c r="O63" s="31"/>
-      <c r="P63" s="31"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="32"/>
+      <c r="M63" s="32"/>
+      <c r="N63" s="32"/>
+      <c r="O63" s="32"/>
+      <c r="P63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
+      <c r="A64" s="29" t="s">
+        <v>419</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="B65" s="32">
+      <c r="A65" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="B65" s="33">
         <v>1.48</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>1.15</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>1.63</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>3.12</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="33">
         <v>5.27</v>
       </c>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="31"/>
-      <c r="O65" s="31"/>
-      <c r="P65" s="31"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
+      <c r="L65" s="32"/>
+      <c r="M65" s="32"/>
+      <c r="N65" s="32"/>
+      <c r="O65" s="32"/>
+      <c r="P65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="B66" s="32">
+      <c r="A66" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="B66" s="33">
         <v>2.3</v>
       </c>
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="31"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="31"/>
-      <c r="K66" s="31"/>
-      <c r="L66" s="31"/>
-      <c r="M66" s="31"/>
-      <c r="N66" s="31"/>
-      <c r="O66" s="31"/>
-      <c r="P66" s="31"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="32"/>
+      <c r="L66" s="32"/>
+      <c r="M66" s="32"/>
+      <c r="N66" s="32"/>
+      <c r="O66" s="32"/>
+      <c r="P66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>421</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
+      <c r="A67" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="B68" s="32">
+      <c r="A68" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="B68" s="33">
         <v>2.11</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="33">
         <v>1.26</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="33">
         <v>1.71</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>3.08</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="33">
         <v>6.08</v>
       </c>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="31"/>
-      <c r="J68" s="31"/>
-      <c r="K68" s="31"/>
-      <c r="L68" s="31"/>
-      <c r="M68" s="31"/>
-      <c r="N68" s="31"/>
-      <c r="O68" s="31"/>
-      <c r="P68" s="31"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
+      <c r="L68" s="32"/>
+      <c r="M68" s="32"/>
+      <c r="N68" s="32"/>
+      <c r="O68" s="32"/>
+      <c r="P68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="B69" s="32">
+      <c r="A69" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="B69" s="33">
         <v>2.61</v>
       </c>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="31"/>
-      <c r="K69" s="31"/>
-      <c r="L69" s="31"/>
-      <c r="M69" s="31"/>
-      <c r="N69" s="31"/>
-      <c r="O69" s="31"/>
-      <c r="P69" s="31"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="32"/>
+      <c r="M69" s="32"/>
+      <c r="N69" s="32"/>
+      <c r="O69" s="32"/>
+      <c r="P69" s="32"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>424</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
+      <c r="A70" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="32">
+      <c r="A71" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B71" s="32"/>
+      <c r="C71" s="33">
         <v>25.46</v>
       </c>
-      <c r="D71" s="32">
+      <c r="D71" s="33">
         <v>19.86</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="33">
         <v>69.67</v>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="33">
         <v>27.8</v>
       </c>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
-      <c r="M71" s="31"/>
-      <c r="N71" s="31"/>
-      <c r="O71" s="31"/>
-      <c r="P71" s="31"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="32"/>
+      <c r="M71" s="32"/>
+      <c r="N71" s="32"/>
+      <c r="O71" s="32"/>
+      <c r="P71" s="32"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="B72" s="32">
+      <c r="A72" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="B72" s="33">
         <v>57.07</v>
       </c>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
-      <c r="K72" s="31"/>
-      <c r="L72" s="31"/>
-      <c r="M72" s="31"/>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
+      <c r="L72" s="32"/>
+      <c r="M72" s="32"/>
+      <c r="N72" s="32"/>
+      <c r="O72" s="32"/>
+      <c r="P72" s="32"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
